--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487973_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487973_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1299</v>
+        <v>1.9772</v>
       </c>
       <c r="E2" t="n">
-        <v>1.339</v>
+        <v>1.1582</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7909</v>
+        <v>0.819</v>
       </c>
       <c r="G2" t="n">
         <v>-0.0177</v>
@@ -610,13 +610,13 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4996</v>
+        <v>0.3469</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1906</v>
+        <v>-0.3715</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6903</v>
+        <v>0.7183</v>
       </c>
       <c r="V2" t="n">
         <v>4.2249</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. ALMAGRO LAZARO</t>
+          <t>J. MORALES MUNOZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2891</v>
+        <v>0.3511</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5717</v>
+        <v>-0.4438</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2826</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.277</v>
+        <v>0.5873</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1909</v>
+        <v>-2.9981</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0861</v>
+        <v>3.5854</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0085</v>
+        <v>0.6786</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9282</v>
+        <v>-2.3464</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0804</v>
+        <v>3.025</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7315</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7372</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0057</v>
+        <v>0.5604</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9911</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3293</v>
+        <v>-0.4433</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5543</v>
+        <v>-0.6138</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2251</v>
+        <v>0.1705</v>
       </c>
       <c r="V3" t="n">
-        <v>0.674</v>
+        <v>0.6036</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X3" t="n">
-        <v>0.674</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MORALES MUNOZ</t>
+          <t>R. ALMAGRO LAZARO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0602</v>
+        <v>-0.2026</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.0155</v>
+        <v>0.1643</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0757</v>
+        <v>-0.3669</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5873</v>
+        <v>0.277</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.9981</v>
+        <v>0.1909</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5854</v>
+        <v>0.0861</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6786</v>
+        <v>1.0085</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.3464</v>
+        <v>0.9282</v>
       </c>
       <c r="L4" t="n">
-        <v>3.025</v>
+        <v>0.0804</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.7315</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.7372</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5604</v>
+        <v>0.0057</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3964</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7343</v>
+        <v>-0.1625</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1855</v>
+        <v>0.1469</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4513</v>
+        <v>-0.3093</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6036</v>
+        <v>0.674</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8701</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ESPINAL REYNOSO</t>
+          <t>A. TORIL RAYO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9177</v>
+        <v>-1.2169</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3346</v>
+        <v>-1.8189</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.2523</v>
+        <v>0.602</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7143</v>
+        <v>-0.8484</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1683</v>
+        <v>-2.2181</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5459</v>
+        <v>1.3697</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3423</v>
+        <v>-1.1664</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2983</v>
+        <v>-1.9699</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0441</v>
+        <v>0.8036</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.0566</v>
+        <v>0.318</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4666</v>
+        <v>-0.2481</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.59</v>
+        <v>0.5661</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9244</v>
+        <v>-0.2386</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1727</v>
+        <v>-0.1439</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7517</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0704</v>
+        <v>0.2666</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8107</v>
+        <v>1.4737</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7403</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TORIL RAYO</t>
+          <t>J. ESPINAL REYNOSO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7524</v>
+        <v>-1.3189</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0455</v>
+        <v>1.9895</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2931</v>
+        <v>-3.3085</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8484</v>
+        <v>-1.7143</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2181</v>
+        <v>-0.1683</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3697</v>
+        <v>-1.5459</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1664</v>
+        <v>1.3423</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.9699</v>
+        <v>1.2983</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8036</v>
+        <v>0.0441</v>
       </c>
       <c r="M6" t="n">
-        <v>0.318</v>
+        <v>-3.0566</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2481</v>
+        <v>-1.4666</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5661</v>
+        <v>-1.59</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3964</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7742</v>
+        <v>0.5231</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3706</v>
+        <v>-0.1724</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4036</v>
+        <v>0.6955</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2666</v>
+        <v>0.0704</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4737</v>
+        <v>1.8107</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2071</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.7795</v>
+        <v>-1.6214</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0757</v>
+        <v>-0.9739</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7037</v>
+        <v>-0.6476</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0218</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7665</v>
+        <v>-0.6085</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6417</v>
+        <v>-0.5855</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. VIVERO RODRIGUEZ</t>
+          <t>J. MARTINEZ GUZMAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0055</v>
+        <v>-1.9997</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9308</v>
+        <v>-3.139</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0746</v>
+        <v>1.1393</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.5732</v>
+        <v>-0.369</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.6427</v>
+        <v>-0.9926</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0695</v>
+        <v>0.6237</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5259</v>
+        <v>-1.9369</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.3818</v>
+        <v>-1.3381</v>
       </c>
       <c r="L8" t="n">
-        <v>1.856</v>
+        <v>-0.5988</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0474</v>
+        <v>1.5679</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2609</v>
+        <v>0.3455</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7864</v>
+        <v>1.2224</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3964</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7749</v>
+        <v>-0.168</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3196</v>
+        <v>-0.211</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4553</v>
+        <v>0.043</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6036</v>
+        <v>-1.0663</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8701</v>
+        <v>-1.0663</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. JIMENEZ MARTINEZ</t>
+          <t>U. GARCES BENITEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1796</v>
+        <v>-2.1787</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9556</v>
+        <v>-0.858</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.224</v>
+        <v>-1.3206</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2199</v>
+        <v>-2.198</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1723</v>
+        <v>-0.4493</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3922</v>
+        <v>-1.7486</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4099</v>
+        <v>-0.659</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2894</v>
+        <v>0.0202</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1205</v>
+        <v>-0.6791</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.19</v>
+        <v>-1.539</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4617</v>
+        <v>-0.4695</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2717</v>
+        <v>-1.0695</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1982</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1329</v>
+        <v>0.0193</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3744</v>
+        <v>-0.1991</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2415</v>
+        <v>0.2184</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MARTINEZ GUZMAN</t>
+          <t>F. JIMENEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1816</v>
+        <v>-2.2357</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4051</v>
+        <v>-0.9556</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2235</v>
+        <v>-1.2802</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.369</v>
+        <v>0.2199</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9926</v>
+        <v>-0.1723</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6237</v>
+        <v>0.3922</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9369</v>
+        <v>0.4099</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3381</v>
+        <v>0.2894</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5988</v>
+        <v>0.1205</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5679</v>
+        <v>-0.19</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3455</v>
+        <v>-0.4617</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2224</v>
+        <v>0.2717</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3964</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3499</v>
+        <v>-0.1891</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4771</v>
+        <v>-0.3744</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1272</v>
+        <v>0.1853</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0663</v>
+        <v>-1.4737</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0663</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>U. GARCES BENITEZ</t>
+          <t>I. VIVERO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2244</v>
+        <v>-2.3267</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9599</v>
+        <v>-2.1117</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2645</v>
+        <v>-0.215</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.198</v>
+        <v>-3.5732</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4493</v>
+        <v>-4.6427</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7486</v>
+        <v>1.0695</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.659</v>
+        <v>-1.5259</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0202</v>
+        <v>-3.3818</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6791</v>
+        <v>1.856</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.539</v>
+        <v>-2.0474</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4695</v>
+        <v>-1.2609</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0695</v>
+        <v>-0.7864</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0264</v>
+        <v>1.4537</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.301</v>
+        <v>0.1388</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2745</v>
+        <v>1.3149</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3692</v>
+        <v>-4.0365</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3405</v>
+        <v>-3.1762</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0287</v>
+        <v>-0.8602</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3927</v>
@@ -1390,13 +1390,13 @@
         <v>0.1982</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3134</v>
+        <v>0.0193</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3523</v>
+        <v>-0.1881</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0389</v>
+        <v>0.2074</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8701</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.928800000000001</v>
+        <v>-8.426600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.0303</v>
+        <v>-6.7247</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8985</v>
+        <v>-1.702</v>
       </c>
       <c r="G13" t="n">
         <v>-4.7723</v>
@@ -1468,13 +1468,13 @@
         <v>0.1982</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7888</v>
+        <v>-1.2866</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8625</v>
+        <v>-0.5569</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9263</v>
+        <v>-0.7297</v>
       </c>
       <c r="V13" t="n">
         <v>0.4074</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-23.8595</v>
+        <v>-23.2354</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.5136</v>
+        <v>-16.8898</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.3457</v>
+        <v>-6.3458</v>
       </c>
       <c r="G14" t="n">
         <v>-14.8232</v>
@@ -1516,13 +1516,13 @@
         <v>-15.5024</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6793000000000005</v>
+        <v>0.6792999999999996</v>
       </c>
       <c r="J14" t="n">
         <v>-5.7309</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.5683</v>
+        <v>-7.568300000000001</v>
       </c>
       <c r="L14" t="n">
         <v>1.838</v>
@@ -1531,7 +1531,7 @@
         <v>-9.092499999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.933699999999999</v>
+        <v>-7.9337</v>
       </c>
       <c r="O14" t="n">
         <v>-1.1587</v>
@@ -1543,22 +1543,22 @@
         <v>-17.8399</v>
       </c>
       <c r="R14" t="n">
-        <v>7.929</v>
+        <v>7.928999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3582</v>
+        <v>-0.7343000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.1922</v>
+        <v>-2.5683</v>
       </c>
       <c r="U14" t="n">
-        <v>1.834000000000001</v>
+        <v>1.8341</v>
       </c>
       <c r="V14" t="n">
-        <v>2.233200000000001</v>
+        <v>2.2332</v>
       </c>
       <c r="W14" t="n">
-        <v>9.249599999999999</v>
+        <v>9.249600000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-7.016299999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9456</v>
+        <v>7.0742</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0276</v>
+        <v>4.8239</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9179</v>
+        <v>2.2503</v>
       </c>
       <c r="G15" t="n">
         <v>4.4664</v>
@@ -1624,13 +1624,13 @@
         <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0451</v>
+        <v>0.0835</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0072</v>
+        <v>-0.211</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0379</v>
+        <v>0.2945</v>
       </c>
       <c r="V15" t="n">
         <v>1.1367</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8022</v>
+        <v>6.177</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1461</v>
+        <v>3.5536</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6561</v>
+        <v>2.6234</v>
       </c>
       <c r="G16" t="n">
         <v>5.3163</v>
@@ -1702,13 +1702,13 @@
         <v>2.3787</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8759</v>
+        <v>-0.5011</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4975</v>
+        <v>-1.0901</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6216</v>
+        <v>0.589</v>
       </c>
       <c r="V16" t="n">
         <v>1.9565</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.6052</v>
+        <v>4.7707</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3085</v>
+        <v>0.5954</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2967</v>
+        <v>4.1752</v>
       </c>
       <c r="G17" t="n">
         <v>2.7386</v>
@@ -1780,13 +1780,13 @@
         <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3441</v>
+        <v>1.5096</v>
       </c>
       <c r="T17" t="n">
-        <v>1.039</v>
+        <v>0.3259</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3051</v>
+        <v>1.1837</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8651</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.9087</v>
+        <v>4.1244</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4995</v>
+        <v>0.8883</v>
       </c>
       <c r="F18" t="n">
-        <v>3.4091</v>
+        <v>3.2361</v>
       </c>
       <c r="G18" t="n">
         <v>0.6815</v>
@@ -1858,13 +1858,13 @@
         <v>2.3787</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7029</v>
+        <v>0.9186</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7894</v>
+        <v>0.1782</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9134</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>1.1367</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.802</v>
+        <v>1.4402</v>
       </c>
       <c r="E19" t="n">
-        <v>1.727</v>
+        <v>1.4214</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0188</v>
       </c>
       <c r="G19" t="n">
         <v>0.7065</v>
@@ -1936,13 +1936,13 @@
         <v>0.1982</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6307</v>
+        <v>0.2689</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4919</v>
+        <v>0.1863</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1387</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0.2666</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6581</v>
+        <v>1.3512</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0769</v>
+        <v>-0.6881</v>
       </c>
       <c r="F20" t="n">
-        <v>1.735</v>
+        <v>2.0393</v>
       </c>
       <c r="G20" t="n">
         <v>1.4973</v>
@@ -2014,13 +2014,13 @@
         <v>2.5769</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7732</v>
+        <v>0.4663</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8518</v>
+        <v>0.2406</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.2256</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2071</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. AGÜERA ZEA</t>
+          <t>F. LASCORZ RIVARES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2053</v>
+        <v>1.2667</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2053</v>
+        <v>0.655</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.6117</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2053</v>
+        <v>0.743</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.2348</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2053</v>
+        <v>-0.4917</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2053</v>
+        <v>1.0692</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1.0291</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2053</v>
+        <v>0.0402</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-0.3262</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.2057</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.5319</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.2065</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.2598</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-0.0533</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. LASCORZ RIVARES</t>
+          <t>J. AGÜERA ZEA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8135</v>
+        <v>1.2053</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1457</v>
+        <v>1.2053</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6677999999999999</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.743</v>
+        <v>1.2053</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2348</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4917</v>
+        <v>1.2053</v>
       </c>
       <c r="J22" t="n">
-        <v>1.0692</v>
+        <v>1.2053</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0291</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0402</v>
+        <v>1.2053</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3262</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2057</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5319</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2467</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2496</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0029</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. LÓPEZ GÓMEZ</t>
+          <t>J. AGUERA ZEA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3027</v>
+        <v>0.7614</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3027</v>
+        <v>-1.6869</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>2.4483</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3027</v>
+        <v>-1.2994</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3027</v>
+        <v>0.4301</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-1.7295</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3027</v>
+        <v>-1.7471</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3027</v>
+        <v>-0.3966</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.3505</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>0.4478</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.8267</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-0.379</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.7433</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.2063</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.9497</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.0612</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. AGUERA ZEA</t>
+          <t>P. LÓPEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2305</v>
+        <v>0.3027</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6037</v>
+        <v>0.3027</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3732</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2994</v>
+        <v>0.3027</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4301</v>
+        <v>0.3027</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7295</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.7471</v>
+        <v>0.3027</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3966</v>
+        <v>0.3027</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3505</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4478</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8267</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.379</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2486</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1232</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8746</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0612</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.0031</v>
+        <v>0.2213</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6652</v>
+        <v>-0.054</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3379</v>
+        <v>0.2753</v>
       </c>
       <c r="G25" t="n">
         <v>0.9653</v>
@@ -2404,13 +2404,13 @@
         <v>1.5858</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2858</v>
+        <v>-0.0614</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1232</v>
+        <v>-0.5119</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1627</v>
+        <v>0.4505</v>
       </c>
       <c r="V25" t="n">
         <v>-2.2684</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.7233</v>
+        <v>-1.4366</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.0611</v>
+        <v>-3.163</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3379</v>
+        <v>1.7264</v>
       </c>
       <c r="G26" t="n">
         <v>-0.473</v>
@@ -2482,13 +2482,13 @@
         <v>1.9822</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.863</v>
+        <v>-0.5763</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6936</v>
+        <v>-0.7955</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1694</v>
+        <v>0.2192</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3873</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.2269</v>
+        <v>-2.0408</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.6097</v>
+        <v>-1.5078</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6172</v>
+        <v>-0.5329</v>
       </c>
       <c r="G27" t="n">
         <v>-2.0275</v>
@@ -2560,13 +2560,13 @@
         <v>0.5947</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.5275</v>
+        <v>-0.3414</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.312</v>
+        <v>-0.2101</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2155</v>
+        <v>-0.1313</v>
       </c>
       <c r="V27" t="n">
         <v>-0.2666</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>23.8595</v>
+        <v>25.2177</v>
       </c>
       <c r="E28" t="n">
         <v>6.345800000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>17.5135</v>
+        <v>18.8719</v>
       </c>
       <c r="G28" t="n">
         <v>14.823</v>
@@ -2638,13 +2638,13 @@
         <v>17.8402</v>
       </c>
       <c r="S28" t="n">
-        <v>1.358300000000001</v>
+        <v>2.7165</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.8342</v>
+        <v>-1.8341</v>
       </c>
       <c r="U28" t="n">
-        <v>3.192099999999999</v>
+        <v>4.550599999999999</v>
       </c>
       <c r="V28" t="n">
         <v>-2.233200000000001</v>
